--- a/artfynd/A 58161-2025 artfynd.xlsx
+++ b/artfynd/A 58161-2025 artfynd.xlsx
@@ -823,7 +823,7 @@
         <v>137172150</v>
       </c>
       <c r="B3" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>137172121</v>
       </c>
       <c r="B4" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>137172122</v>
       </c>
       <c r="B5" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58161-2025 artfynd.xlsx
+++ b/artfynd/A 58161-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172125</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>137172150</v>
       </c>
       <c r="B3" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>137172121</v>
       </c>
       <c r="B4" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>137172122</v>
       </c>
       <c r="B5" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58161-2025 artfynd.xlsx
+++ b/artfynd/A 58161-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172125</v>
       </c>
       <c r="B2" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>137172150</v>
       </c>
       <c r="B3" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>137172121</v>
       </c>
       <c r="B4" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>137172122</v>
       </c>
       <c r="B5" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58161-2025 artfynd.xlsx
+++ b/artfynd/A 58161-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172125</v>
       </c>
       <c r="B2" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>137172150</v>
       </c>
       <c r="B3" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>137172121</v>
       </c>
       <c r="B4" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>137172122</v>
       </c>
       <c r="B5" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58161-2025 artfynd.xlsx
+++ b/artfynd/A 58161-2025 artfynd.xlsx
@@ -710,11 +710,7 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -850,11 +846,7 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -966,11 +958,7 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1082,11 +1070,7 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">

--- a/artfynd/A 58161-2025 artfynd.xlsx
+++ b/artfynd/A 58161-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172125</v>
       </c>
       <c r="B2" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137172150</v>
       </c>
       <c r="B3" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137172121</v>
       </c>
       <c r="B4" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137172122</v>
       </c>
       <c r="B5" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58161-2025 artfynd.xlsx
+++ b/artfynd/A 58161-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172125</v>
       </c>
       <c r="B2" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137172150</v>
       </c>
       <c r="B3" t="n">
-        <v>108421</v>
+        <v>108442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137172121</v>
       </c>
       <c r="B4" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137172122</v>
       </c>
       <c r="B5" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58161-2025 artfynd.xlsx
+++ b/artfynd/A 58161-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172125</v>
       </c>
       <c r="B2" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137172150</v>
       </c>
       <c r="B3" t="n">
-        <v>108442</v>
+        <v>108443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137172121</v>
       </c>
       <c r="B4" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137172122</v>
       </c>
       <c r="B5" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58161-2025 artfynd.xlsx
+++ b/artfynd/A 58161-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172125</v>
       </c>
       <c r="B2" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137172150</v>
       </c>
       <c r="B3" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137172121</v>
       </c>
       <c r="B4" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137172122</v>
       </c>
       <c r="B5" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58161-2025 artfynd.xlsx
+++ b/artfynd/A 58161-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172125</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137172150</v>
       </c>
       <c r="B3" t="n">
-        <v>108448</v>
+        <v>108451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137172121</v>
       </c>
       <c r="B4" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137172122</v>
       </c>
       <c r="B5" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58161-2025 artfynd.xlsx
+++ b/artfynd/A 58161-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172125</v>
       </c>
       <c r="B2" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137172150</v>
       </c>
       <c r="B3" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137172121</v>
       </c>
       <c r="B4" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137172122</v>
       </c>
       <c r="B5" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58161-2025 artfynd.xlsx
+++ b/artfynd/A 58161-2025 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>137172150</v>
       </c>
       <c r="B3" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137172121</v>
       </c>
       <c r="B4" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137172122</v>
       </c>
       <c r="B5" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58161-2025 artfynd.xlsx
+++ b/artfynd/A 58161-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172125</v>
       </c>
       <c r="B2" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137172150</v>
       </c>
       <c r="B3" t="n">
-        <v>108458</v>
+        <v>108470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137172121</v>
       </c>
       <c r="B4" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137172122</v>
       </c>
       <c r="B5" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58161-2025 artfynd.xlsx
+++ b/artfynd/A 58161-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172125</v>
       </c>
       <c r="B2" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137172150</v>
       </c>
       <c r="B3" t="n">
-        <v>108470</v>
+        <v>108471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137172121</v>
       </c>
       <c r="B4" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137172122</v>
       </c>
       <c r="B5" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58161-2025 artfynd.xlsx
+++ b/artfynd/A 58161-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172125</v>
       </c>
       <c r="B2" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137172150</v>
       </c>
       <c r="B3" t="n">
-        <v>108471</v>
+        <v>108474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137172121</v>
       </c>
       <c r="B4" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137172122</v>
       </c>
       <c r="B5" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58161-2025 artfynd.xlsx
+++ b/artfynd/A 58161-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172125</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137172150</v>
       </c>
       <c r="B3" t="n">
-        <v>108474</v>
+        <v>108480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137172121</v>
       </c>
       <c r="B4" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137172122</v>
       </c>
       <c r="B5" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
